--- a/data/btc_merged_daily.xlsx
+++ b/data/btc_merged_daily.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4248"/>
+  <dimension ref="A1:C4315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55652,9 +55652,880 @@
         <v>46220</v>
       </c>
       <c r="B4248" t="n">
-        <v>63965.390625</v>
+        <v>63900.18</v>
       </c>
       <c r="C4248" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4249">
+      <c r="A4249" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B4249" t="n">
+        <v>64793.76</v>
+      </c>
+      <c r="C4249" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4250">
+      <c r="A4250" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B4250" t="n">
+        <v>64571.18</v>
+      </c>
+      <c r="C4250" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4251">
+      <c r="A4251" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B4251" t="n">
+        <v>65151.3</v>
+      </c>
+      <c r="C4251" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4252">
+      <c r="A4252" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B4252" t="n">
+        <v>66553.73</v>
+      </c>
+      <c r="C4252" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4253">
+      <c r="A4253" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B4253" t="n">
+        <v>66063.67</v>
+      </c>
+      <c r="C4253" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4254">
+      <c r="A4254" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B4254" t="n">
+        <v>65000.99</v>
+      </c>
+      <c r="C4254" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4255">
+      <c r="A4255" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B4255" t="n">
+        <v>64108.38</v>
+      </c>
+      <c r="C4255" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4256">
+      <c r="A4256" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B4256" t="n">
+        <v>64319.9</v>
+      </c>
+      <c r="C4256" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4257">
+      <c r="A4257" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B4257" t="n">
+        <v>65243.31</v>
+      </c>
+      <c r="C4257" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4258">
+      <c r="A4258" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4258" t="n">
+        <v>63692.68</v>
+      </c>
+      <c r="C4258" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4259">
+      <c r="A4259" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B4259" t="n">
+        <v>63945.6</v>
+      </c>
+      <c r="C4259" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4260">
+      <c r="A4260" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B4260" t="n">
+        <v>63896.15</v>
+      </c>
+      <c r="C4260" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4261">
+      <c r="A4261" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B4261" t="n">
+        <v>64817.71</v>
+      </c>
+      <c r="C4261" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4262">
+      <c r="A4262" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B4262" t="n">
+        <v>62886.64</v>
+      </c>
+      <c r="C4262" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4263">
+      <c r="A4263" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B4263" t="n">
+        <v>62835</v>
+      </c>
+      <c r="C4263" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4264">
+      <c r="A4264" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B4264" t="n">
+        <v>63443.93</v>
+      </c>
+      <c r="C4264" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4265">
+      <c r="A4265" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B4265" t="n">
+        <v>63503.04</v>
+      </c>
+      <c r="C4265" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4266">
+      <c r="A4266" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B4266" t="n">
+        <v>64023.39</v>
+      </c>
+      <c r="C4266" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4267">
+      <c r="A4267" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B4267" t="n">
+        <v>64555.45</v>
+      </c>
+      <c r="C4267" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4268">
+      <c r="A4268" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B4268" t="n">
+        <v>64291.84</v>
+      </c>
+      <c r="C4268" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4269">
+      <c r="A4269" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B4269" t="n">
+        <v>64877.34</v>
+      </c>
+      <c r="C4269" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4270">
+      <c r="A4270" s="2" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B4270" t="n">
+        <v>64910.12</v>
+      </c>
+      <c r="C4270" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4271">
+      <c r="A4271" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B4271" t="n">
+        <v>64855.5</v>
+      </c>
+      <c r="C4271" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4272">
+      <c r="A4272" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B4272" t="n">
+        <v>63876.26</v>
+      </c>
+      <c r="C4272" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4273">
+      <c r="A4273" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B4273" t="n">
+        <v>63528.48</v>
+      </c>
+      <c r="C4273" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4274">
+      <c r="A4274" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B4274" t="n">
+        <v>63402.49</v>
+      </c>
+      <c r="C4274" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4275">
+      <c r="A4275" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4275" t="n">
+        <v>63387.81</v>
+      </c>
+      <c r="C4275" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4276">
+      <c r="A4276" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B4276" t="n">
+        <v>62968.43</v>
+      </c>
+      <c r="C4276" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4277">
+      <c r="A4277" s="2" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B4277" t="n">
+        <v>62999.01</v>
+      </c>
+      <c r="C4277" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4278">
+      <c r="A4278" s="2" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B4278" t="n">
+        <v>62859.47</v>
+      </c>
+      <c r="C4278" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4279">
+      <c r="A4279" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B4279" t="n">
+        <v>64423.92</v>
+      </c>
+      <c r="C4279" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4280">
+      <c r="A4280" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B4280" t="n">
+        <v>64625.4</v>
+      </c>
+      <c r="C4280" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4281">
+      <c r="A4281" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B4281" t="n">
+        <v>69487.60000000001</v>
+      </c>
+      <c r="C4281" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4282">
+      <c r="A4282" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B4282" t="n">
+        <v>73086.97</v>
+      </c>
+      <c r="C4282" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4283">
+      <c r="A4283" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B4283" t="n">
+        <v>78126.63</v>
+      </c>
+      <c r="C4283" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4284">
+      <c r="A4284" s="2" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B4284" t="n">
+        <v>77117.73</v>
+      </c>
+      <c r="C4284" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4285">
+      <c r="A4285" s="2" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B4285" t="n">
+        <v>77637.69</v>
+      </c>
+      <c r="C4285" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4286">
+      <c r="A4286" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B4286" t="n">
+        <v>78981.39</v>
+      </c>
+      <c r="C4286" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4287">
+      <c r="A4287" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B4287" t="n">
+        <v>78510.95</v>
+      </c>
+      <c r="C4287" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4288">
+      <c r="A4288" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4288" t="n">
+        <v>78961.92999999999</v>
+      </c>
+      <c r="C4288" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4289">
+      <c r="A4289" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B4289" t="n">
+        <v>80209.61</v>
+      </c>
+      <c r="C4289" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4290">
+      <c r="A4290" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B4290" t="n">
+        <v>77838.64999999999</v>
+      </c>
+      <c r="C4290" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4291">
+      <c r="A4291" s="2" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B4291" t="n">
+        <v>78215</v>
+      </c>
+      <c r="C4291" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4292">
+      <c r="A4292" s="2" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B4292" t="n">
+        <v>77757.98</v>
+      </c>
+      <c r="C4292" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4293">
+      <c r="A4293" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B4293" t="n">
+        <v>78603.02</v>
+      </c>
+      <c r="C4293" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4294">
+      <c r="A4294" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B4294" t="n">
+        <v>77392.64999999999</v>
+      </c>
+      <c r="C4294" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4295">
+      <c r="A4295" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B4295" t="n">
+        <v>77330.23</v>
+      </c>
+      <c r="C4295" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4296">
+      <c r="A4296" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B4296" t="n">
+        <v>81129.19</v>
+      </c>
+      <c r="C4296" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4297">
+      <c r="A4297" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B4297" t="n">
+        <v>79658.55</v>
+      </c>
+      <c r="C4297" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4298">
+      <c r="A4298" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B4298" t="n">
+        <v>79879.24000000001</v>
+      </c>
+      <c r="C4298" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4299">
+      <c r="A4299" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B4299" t="n">
+        <v>80309.06</v>
+      </c>
+      <c r="C4299" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4300">
+      <c r="A4300" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B4300" t="n">
+        <v>79067.23</v>
+      </c>
+      <c r="C4300" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4301">
+      <c r="A4301" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B4301" t="n">
+        <v>78548.91</v>
+      </c>
+      <c r="C4301" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4302">
+      <c r="A4302" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B4302" t="n">
+        <v>78303.59</v>
+      </c>
+      <c r="C4302" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4303">
+      <c r="A4303" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B4303" t="n">
+        <v>76664.89</v>
+      </c>
+      <c r="C4303" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4304">
+      <c r="A4304" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B4304" t="n">
+        <v>77276.5</v>
+      </c>
+      <c r="C4304" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4305">
+      <c r="A4305" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B4305" t="n">
+        <v>77270.73</v>
+      </c>
+      <c r="C4305" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4306">
+      <c r="A4306" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B4306" t="n">
+        <v>76804.92</v>
+      </c>
+      <c r="C4306" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4307">
+      <c r="A4307" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B4307" t="n">
+        <v>78200.38</v>
+      </c>
+      <c r="C4307" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4308">
+      <c r="A4308" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B4308" t="n">
+        <v>75656.09</v>
+      </c>
+      <c r="C4308" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4309">
+      <c r="A4309" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B4309" t="n">
+        <v>76208.64</v>
+      </c>
+      <c r="C4309" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4310">
+      <c r="A4310" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B4310" t="n">
+        <v>76366.39999999999</v>
+      </c>
+      <c r="C4310" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4311">
+      <c r="A4311" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B4311" t="n">
+        <v>80844</v>
+      </c>
+      <c r="C4311" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4312">
+      <c r="A4312" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B4312" t="n">
+        <v>81186</v>
+      </c>
+      <c r="C4312" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4313">
+      <c r="A4313" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B4313" t="n">
+        <v>81253.37</v>
+      </c>
+      <c r="C4313" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4314">
+      <c r="A4314" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B4314" t="n">
+        <v>86396.74000000001</v>
+      </c>
+      <c r="C4314" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4315">
+      <c r="A4315" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4315" t="n">
+        <v>85938.03125</v>
+      </c>
+      <c r="C4315" t="inlineStr">
         <is>
           <t>btc_price_fred</t>
         </is>

--- a/data/btc_merged_daily.xlsx
+++ b/data/btc_merged_daily.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4315"/>
+  <dimension ref="A1:C4324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56523,9 +56523,126 @@
         <v>46287</v>
       </c>
       <c r="B4315" t="n">
-        <v>85938.03125</v>
+        <v>86249.98</v>
       </c>
       <c r="C4315" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4316">
+      <c r="A4316" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B4316" t="n">
+        <v>84452.97</v>
+      </c>
+      <c r="C4316" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4317">
+      <c r="A4317" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B4317" t="n">
+        <v>84470.75999999999</v>
+      </c>
+      <c r="C4317" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4318">
+      <c r="A4318" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B4318" t="n">
+        <v>84048.07000000001</v>
+      </c>
+      <c r="C4318" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4319">
+      <c r="A4319" s="2" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B4319" t="n">
+        <v>84337.36</v>
+      </c>
+      <c r="C4319" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4320">
+      <c r="A4320" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B4320" t="n">
+        <v>84553.91</v>
+      </c>
+      <c r="C4320" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4321">
+      <c r="A4321" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B4321" t="n">
+        <v>83487.03</v>
+      </c>
+      <c r="C4321" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4322">
+      <c r="A4322" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4322" t="n">
+        <v>83636.7</v>
+      </c>
+      <c r="C4322" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4323">
+      <c r="A4323" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B4323" t="n">
+        <v>83482.50999999999</v>
+      </c>
+      <c r="C4323" t="inlineStr">
+        <is>
+          <t>btc_price_fred</t>
+        </is>
+      </c>
+    </row>
+    <row r="4324">
+      <c r="A4324" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4324" t="n">
+        <v>83788.078125</v>
+      </c>
+      <c r="C4324" t="inlineStr">
         <is>
           <t>btc_price_fred</t>
         </is>
